--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487793_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487793_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4902</v>
+        <v>5.1715</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0956</v>
+        <v>2.0117</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3946</v>
+        <v>3.1598</v>
       </c>
       <c r="G2" t="n">
         <v>4.3466</v>
@@ -610,13 +610,13 @@
         <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3282</v>
+        <v>0.0095</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0033</v>
+        <v>-0.0871</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3315</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.1911</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3904</v>
+        <v>3.0604</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5797</v>
+        <v>2.0735</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8107</v>
+        <v>0.9869</v>
       </c>
       <c r="G3" t="n">
         <v>1.2917</v>
@@ -688,13 +688,13 @@
         <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9232</v>
+        <v>-0.2531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6524</v>
+        <v>-0.1586</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2707</v>
+        <v>-0.0946</v>
       </c>
       <c r="V3" t="n">
         <v>1.3975</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4869</v>
+        <v>2.3064</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4982</v>
+        <v>2.0182</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9887</v>
+        <v>0.2882</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0604</v>
+        <v>1.6238</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0299</v>
+        <v>-0.5863</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0304</v>
+        <v>2.2101</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5298</v>
+        <v>2.4487</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6096</v>
+        <v>0.5284</v>
       </c>
       <c r="L4" t="n">
         <v>1.9202</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5306</v>
+        <v>-0.8249</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4203</v>
+        <v>-1.1147</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1102</v>
+        <v>0.2898</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5565</v>
+        <v>0.2663</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7829</v>
+        <v>-0.4305</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2264</v>
+        <v>0.6968</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3927</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.265</v>
+        <v>1.7561</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4172</v>
+        <v>0.8849</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1522</v>
+        <v>0.8712</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6238</v>
+        <v>3.0604</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5863</v>
+        <v>1.0299</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2101</v>
+        <v>2.0304</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4487</v>
+        <v>2.5298</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5284</v>
+        <v>0.6096</v>
       </c>
       <c r="L5" t="n">
         <v>1.9202</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8249</v>
+        <v>0.5306</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1147</v>
+        <v>0.4203</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2898</v>
+        <v>0.1102</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7751</v>
+        <v>-0.2872</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0315</v>
+        <v>-0.3962</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2564</v>
+        <v>0.109</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3927</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3927</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1368</v>
+        <v>1.2673</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1108</v>
+        <v>0.2413</v>
       </c>
       <c r="F6" t="n">
         <v>1.026</v>
@@ -922,10 +922,10 @@
         <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3634</v>
+        <v>0.4939</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1866</v>
+        <v>-0.0562</v>
       </c>
       <c r="U6" t="n">
         <v>0.55</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0764</v>
+        <v>1.1965</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3253</v>
+        <v>2.6435</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4017</v>
+        <v>-1.447</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1355</v>
+        <v>1.5939</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2367</v>
+        <v>2.9402</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1012</v>
+        <v>-1.3463</v>
       </c>
       <c r="J7" t="n">
-        <v>0.236</v>
+        <v>2.4637</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4693</v>
+        <v>3.814</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7054</v>
+        <v>-1.3504</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3716</v>
+        <v>-0.8697</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2326</v>
+        <v>-0.8738</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6041</v>
+        <v>0.0041</v>
       </c>
       <c r="P7" t="n">
         <v>0.4162</v>
@@ -1000,28 +1000,28 @@
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6271</v>
+        <v>-1.2347</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2701</v>
+        <v>-0.6338</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3571</v>
+        <v>-0.6008</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8314</v>
+        <v>0.421</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.8314</v>
+        <v>0.8137</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3927</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7408</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>2.364</v>
+        <v>-0.3672</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6232</v>
+        <v>0.9907</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5939</v>
+        <v>-0.1355</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9402</v>
+        <v>-0.2367</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3463</v>
+        <v>0.1012</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4637</v>
+        <v>0.236</v>
       </c>
       <c r="K8" t="n">
-        <v>3.814</v>
+        <v>-0.4693</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3504</v>
+        <v>0.7054</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8697</v>
+        <v>-0.3716</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8738</v>
+        <v>0.2326</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0041</v>
+        <v>-0.6041</v>
       </c>
       <c r="P8" t="n">
         <v>0.4162</v>
@@ -1078,28 +1078,28 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6904</v>
+        <v>1.1742</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9134</v>
+        <v>0.2281</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.777</v>
+        <v>0.946</v>
       </c>
       <c r="V8" t="n">
-        <v>0.421</v>
+        <v>-0.8314</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8137</v>
+        <v>-0.8314</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0223</v>
+        <v>0.2955</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1836</v>
+        <v>-0.5805</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2059</v>
+        <v>0.876</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8809</v>
+        <v>1.8545</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6271</v>
+        <v>1.2732</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7462</v>
+        <v>0.5813</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0501</v>
+        <v>1.4506</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6553</v>
+        <v>1.3388</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7054</v>
+        <v>0.1118</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.931</v>
+        <v>0.4039</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9719</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0408</v>
+        <v>0.4695</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6244</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>0.167</v>
+        <v>-0.5023</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9035</v>
+        <v>-0.3047</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7365</v>
+        <v>-0.1976</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0672</v>
+        <v>-0.6404</v>
       </c>
       <c r="W9" t="n">
-        <v>0.23</v>
+        <v>-0.4776</v>
       </c>
       <c r="X9" t="n">
         <v>-0.1627</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8456</v>
+        <v>-1.0016</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6335</v>
+        <v>0.0282</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7879</v>
+        <v>-1.0298</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8545</v>
+        <v>-0.8809</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2732</v>
+        <v>-1.6271</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5813</v>
+        <v>0.7462</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4506</v>
+        <v>0.0501</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3388</v>
+        <v>-0.6553</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1118</v>
+        <v>0.7054</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4039</v>
+        <v>-0.931</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.9719</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4695</v>
+        <v>0.0408</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6434</v>
+        <v>-0.8122</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3577</v>
+        <v>-0.2519</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2857</v>
+        <v>-0.5604</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6404</v>
+        <v>0.0672</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4776</v>
+        <v>0.23</v>
       </c>
       <c r="X10" t="n">
         <v>-0.1627</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2523</v>
+        <v>-5.2307</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3177</v>
+        <v>-4.0025</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9346</v>
+        <v>-1.2282</v>
       </c>
       <c r="G11" t="n">
         <v>-5.24</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6121</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7854</v>
+        <v>0.1006</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8267</v>
+        <v>0.5331</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.4663</v>
+        <v>9.444900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.9726</v>
+        <v>4.951099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>4.4937</v>
+        <v>4.493799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>9.267099999999997</v>
       </c>
       <c r="H12" t="n">
-        <v>6.9402</v>
+        <v>6.940199999999999</v>
       </c>
       <c r="I12" t="n">
         <v>2.326800000000001</v>
@@ -1375,7 +1375,7 @@
         <v>-1.5121</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8387999999999998</v>
+        <v>-0.8388</v>
       </c>
       <c r="O12" t="n">
         <v>-0.6735000000000002</v>
@@ -1390,16 +1390,16 @@
         <v>6.243699999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4908</v>
+        <v>-0.5119999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.9688</v>
+        <v>-1.9903</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4782</v>
+        <v>1.4781</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6898999999999998</v>
+        <v>0.6899000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>2.4059</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8452</v>
+        <v>1.3504</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6607</v>
+        <v>0.2856</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1844</v>
+        <v>1.0647</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5027</v>
+        <v>0.3882</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1794</v>
+        <v>0.9532</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3233</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6</v>
+        <v>0.1351</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9135</v>
+        <v>0.0959</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3135</v>
+        <v>0.0392</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9027</v>
+        <v>0.2531</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2659</v>
+        <v>0.8572</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6368</v>
+        <v>-0.6041</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>5.582</v>
+        <v>0.3378</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0714</v>
+        <v>0.1505</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5106</v>
+        <v>0.1873</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4422</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3694</v>
+        <v>0.6911</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3928</v>
+        <v>2.1381</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9766</v>
+        <v>-1.447</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3882</v>
+        <v>1.0357</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9532</v>
+        <v>1.2496</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.2139</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1351</v>
+        <v>2.7301</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0959</v>
+        <v>2.4133</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0392</v>
+        <v>0.3167</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2531</v>
+        <v>-1.6944</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8572</v>
+        <v>-1.1637</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6041</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3569</v>
+        <v>-0.5048</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2577</v>
+        <v>-0.8219</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0992</v>
+        <v>0.3171</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.6722</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.9022</v>
       </c>
     </row>
     <row r="15">
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2224</v>
+        <v>-0.5795</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6023</v>
+        <v>-0.5895</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8247</v>
+        <v>0.0101</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0357</v>
+        <v>-2.5027</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2496</v>
+        <v>-2.1794</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2139</v>
+        <v>-0.3233</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7301</v>
+        <v>-0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4133</v>
+        <v>-0.9135</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3167</v>
+        <v>0.3135</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6944</v>
+        <v>-1.9027</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1637</v>
+        <v>-1.2659</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.6368</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4183</v>
+        <v>2.1574</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3577</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0606</v>
+        <v>1.3362</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6722</v>
+        <v>-0.4422</v>
       </c>
       <c r="W16" t="n">
         <v>0.23</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9022</v>
+        <v>-0.6722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3517</v>
+        <v>-0.6496</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2859</v>
+        <v>0.0564</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0658</v>
+        <v>-0.7059</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.181</v>
+        <v>1.728</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2684</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08740000000000001</v>
+        <v>2.6215</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3849</v>
+        <v>2.7121</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1727</v>
+        <v>0.1315</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5576</v>
+        <v>2.5807</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2039</v>
+        <v>-0.9842</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4411</v>
+        <v>-1.025</v>
       </c>
       <c r="O17" t="n">
-        <v>0.645</v>
+        <v>0.0408</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4162</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8971</v>
+        <v>-0.4202</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.901</v>
+        <v>-0.6838</v>
       </c>
       <c r="U17" t="n">
-        <v>0.004</v>
+        <v>0.2637</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6899</v>
+        <v>0.1238</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1498</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6899</v>
+        <v>-1.026</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3773</v>
+        <v>-0.6551</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1644</v>
+        <v>-0.7358</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2129</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5668</v>
@@ -1858,13 +1858,13 @@
         <v>0.4162</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4567</v>
+        <v>0.2655</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2891</v>
+        <v>0.1396</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1677</v>
+        <v>0.1259</v>
       </c>
       <c r="V18" t="n">
         <v>0.23</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9139</v>
+        <v>-0.9255</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8008999999999999</v>
+        <v>0.402</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.113</v>
+        <v>-1.3275</v>
       </c>
       <c r="G19" t="n">
-        <v>1.728</v>
+        <v>-1.3833</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-2.0617</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6215</v>
+        <v>0.6784</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7121</v>
+        <v>0.9767</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1315</v>
+        <v>0.1595</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5807</v>
+        <v>0.8172</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9842</v>
+        <v>-2.3599</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.025</v>
+        <v>-2.2212</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0408</v>
+        <v>-0.1388</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6845</v>
+        <v>0.0675</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5411</v>
+        <v>-0.2209</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1435</v>
+        <v>0.2884</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1238</v>
+        <v>-0.4422</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1498</v>
+        <v>-0.3538</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.026</v>
+        <v>-0.08840000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9756</v>
+        <v>-0.9842</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.241</v>
+        <v>-1.1788</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7346</v>
+        <v>0.1945</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3833</v>
+        <v>-0.181</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0617</v>
+        <v>-0.2684</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6784</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9767</v>
+        <v>-0.3849</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1595</v>
+        <v>0.1727</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8172</v>
+        <v>-0.5576</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3599</v>
+        <v>0.2039</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2212</v>
+        <v>-0.4411</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1388</v>
+        <v>0.645</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9825</v>
+        <v>-0.5296</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8639</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1187</v>
+        <v>0.2643</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4422</v>
+        <v>-0.6899</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1966</v>
+        <v>-2.6443</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2175</v>
+        <v>-0.3183</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4141</v>
+        <v>-2.326</v>
       </c>
       <c r="G21" t="n">
         <v>-5.0084</v>
@@ -2092,13 +2092,13 @@
         <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3165</v>
+        <v>0.8688</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3354</v>
+        <v>0.7996</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0189</v>
+        <v>0.0692</v>
       </c>
       <c r="V21" t="n">
         <v>1.0791</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5083</v>
+        <v>-3.2202</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9853</v>
+        <v>-4.6639</v>
       </c>
       <c r="F22" t="n">
-        <v>1.477</v>
+        <v>1.4437</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2631</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3503</v>
+        <v>-0.0621</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8234</v>
+        <v>-0.5019</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4731</v>
+        <v>0.4398</v>
       </c>
       <c r="V22" t="n">
         <v>-0.23</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.466200000000001</v>
+        <v>-7.7519</v>
       </c>
       <c r="E23" t="n">
         <v>-4.2638</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2025</v>
+        <v>-3.488100000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-9.266999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.9402</v>
+        <v>-6.940200000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-2.3269</v>
@@ -2227,7 +2227,7 @@
         <v>0.8387999999999998</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6734000000000007</v>
+        <v>0.6734000000000002</v>
       </c>
       <c r="M23" t="n">
         <v>-10.7792</v>
@@ -2239,7 +2239,7 @@
         <v>-3.000299999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="Q23" t="n">
         <v>-6.2436</v>
@@ -2248,13 +2248,13 @@
         <v>6.243499999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>1.4908</v>
+        <v>2.2051</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4784</v>
+        <v>-1.4783</v>
       </c>
       <c r="U23" t="n">
-        <v>2.969000000000001</v>
+        <v>3.6834</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6898</v>
